--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Area Under Cultivation - Foodgrains.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Area Under Cultivation - Foodgrains.xlsx
@@ -269,7 +269,7 @@
     <t>(Lakhs Hectares)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note : Data for 2025-26 is based on First Advance Estimates.
+    <t xml:space="preserve">Note     : Data for 2025-26 are based on Third Advance Estimates.
 Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India.</t>
   </si>
 </sst>
@@ -482,11 +482,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:I87"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="14.5455986666667" customWidth="1"/>
     <col min="3" max="8" width="15.5457" customWidth="1"/>
+    <col min="9" max="9" width="84512e-6" customWidth="1"/>
+    <col min="10" max="10" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -497,12 +499,14 @@
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="12.7992" customHeight="1">
       <c r="B4" s="15" t="s">
         <v>85</v>
       </c>
+      <c r="C4" s="15"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="6.9329" customHeight="1"/>
     <row r="6" s="1" customFormat="1" ht="39.9975" customHeight="1">
@@ -567,20 +571,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="10">
-        <v>441.7</v>
-      </c>
-      <c r="D9" s="10"/>
+        <v>528.32</v>
+      </c>
+      <c r="D9" s="10">
+        <v>336</v>
+      </c>
       <c r="E9" s="10">
-        <v>191.1</v>
+        <v>272.47</v>
       </c>
       <c r="F9" s="10">
-        <v>632.8</v>
+        <v>1136.79</v>
       </c>
       <c r="G9" s="10">
-        <v>109.35</v>
+        <v>286.46</v>
       </c>
       <c r="H9" s="10">
-        <v>742.15</v>
+        <v>1423.25</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -2318,12 +2324,16 @@
       <c r="E86" s="16"/>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
-    </row>
+      <c r="H86" s="16"/>
+      <c r="I86" s="16"/>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:E2"/>
+  <mergeCells count="5">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B86:G86"/>
+    <mergeCell ref="B86:I86"/>
     <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageSetup paperSize="120" scale="100" orientation="portrait"/>
